--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -624,16 +624,16 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-70% pred | 70% hist
-[PINNED]</t>
+75% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Pranjali Jain
-13% pred | 13% hist
-[CONSIDER]</t>
+18% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D3" s="7" t="n"/>
@@ -648,46 +648,32 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-43% pred | 43% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
-82% pred | 82% hist
-[PINNED]</t>
+82% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Strength Lab
 Anisha Shah
-66% pred | 66% hist
-[PINNED]</t>
+70% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
-89% pred | 89% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Mrigakshi Jaiswal
-32% pred | 32% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+89% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
@@ -700,9 +686,9 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-32% pred | 32% hist
-[CONSIDER]</t>
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -710,8 +696,8 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-87% pred | 87% hist
-[PINNED]</t>
+84% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -719,8 +705,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 33% hist
-[INCLUDE]</t>
+33% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
@@ -732,25 +718,25 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-90% pred | 90% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n"/>
+90% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simran Dutt
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
     </row>
@@ -764,28 +750,21 @@
         <is>
           <t>Mat 57
 Atulan Purohit
-57% pred | 57% hist
-[PINNED]</t>
+57% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-40% pred | 40% hist
-[INCLUDE]</t>
+40% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
@@ -801,13 +780,20 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-69% pred | 69% hist
-[PROTECT_EXACT]</t>
+68% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
@@ -820,8 +806,8 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 64% hist
-[CONSIDER]</t>
+60% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -829,18 +815,18 @@
         <is>
           <t>Back Body Blaze
 Anisha Shah
-60% pred | 60% hist
-[PINNED]</t>
+60% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
 Rohan Dahima
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
+63% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H9" s="7" t="n"/>
@@ -853,20 +839,13 @@
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
 Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
+61% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="F10" s="7" t="n"/>
@@ -882,20 +861,13 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-18% pred | 18% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E11" s="7" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-40% pred | 40% hist
-[INCLUDE]</t>
+          <t>FIT
+Mrigakshi Jaiswal
+65% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
@@ -910,28 +882,35 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
+          <t>Barre 57
+Pranjali Jain
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Anisha Shah
-18% pred | 18% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
+Simran Dutt
+35% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-57% pred | 57% hist
-[PROTECT_EXACT]</t>
+62% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H12" s="7" t="n"/>
@@ -943,31 +922,38 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-54% pred | 54% hist
-[INCLUDE]</t>
+45% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-75% pred | 75% hist
-[PINNED]</t>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Rohan Dahima
-43% pred | 43% hist
-[PINNED]</t>
+45% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
@@ -982,25 +968,25 @@
         <is>
           <t>Mat 57
 Anisha Shah
-65% pred | 65% hist
-[PINNED]</t>
+65% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
-20% pred | 20% hist
-[CONSIDER]</t>
+0% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
+61% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
@@ -1016,13 +1002,20 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
@@ -1037,155 +1030,225 @@
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+          <t>FIT
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-73% pred | 73% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-52% pred | 52% hist
-[PROTECT]</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+40% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>12:15</t>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Anmol Sharma
+71% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
+          <t>Barre 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
+Anisha Shah
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Karan Bhatia
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Richard D'Costa
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Simran Dutt
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Bret Saldanha
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -1194,51 +1257,37 @@
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-41% pred | 41% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simran Dutt
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-44% pred | 44% hist
-[PINNED]</t>
+[]</t>
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -1247,233 +1296,79 @@
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Anisha Shah
-40% pred | 40% hist
-[PROTECT_EXACT]</t>
+28% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Simran Dutt
-29% pred | 29% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+          <t>Barre 57
+Raunak Khemuka
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Anmol Sharma
+          <t>Cardio Barre
+Siddhartha Kusuma
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Mrigakshi Jaiswal
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simonelle De Vitre
-34% pred | 34% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Karan Bhatia
-26% pred | 26% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-44% pred | 44% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-26% pred | 26% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simran Dutt
-83% pred | 83% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-39% pred | 39% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-62% pred | 62% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-22% pred | 22% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1489,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1568,16 +1463,16 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-70% pred | 70% hist
-[PINNED]</t>
+75% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Pranjali Jain
-13% pred | 13% hist
-[CONSIDER]</t>
+18% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D3" s="7" t="n"/>
@@ -1592,46 +1487,32 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-43% pred | 43% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
-82% pred | 82% hist
-[PINNED]</t>
+82% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Strength Lab
 Anisha Shah
-66% pred | 66% hist
-[PINNED]</t>
+70% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
-89% pred | 89% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Mrigakshi Jaiswal
-32% pred | 32% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+89% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
@@ -1644,9 +1525,9 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-32% pred | 32% hist
-[CONSIDER]</t>
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -1654,8 +1535,8 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-87% pred | 87% hist
-[PINNED]</t>
+84% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -1663,8 +1544,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 33% hist
-[INCLUDE]</t>
+33% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
@@ -1676,25 +1557,25 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-90% pred | 90% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n"/>
+90% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simran Dutt
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
     </row>
@@ -1708,28 +1589,21 @@
         <is>
           <t>Mat 57
 Atulan Purohit
-57% pred | 57% hist
-[PINNED]</t>
+57% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-40% pred | 40% hist
-[INCLUDE]</t>
+40% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
@@ -1745,13 +1619,20 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-69% pred | 69% hist
-[PROTECT_EXACT]</t>
+68% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
@@ -1764,8 +1645,8 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 64% hist
-[CONSIDER]</t>
+60% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -1773,18 +1654,18 @@
         <is>
           <t>Back Body Blaze
 Anisha Shah
-60% pred | 60% hist
-[PINNED]</t>
+60% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
 Rohan Dahima
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
+63% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H9" s="7" t="n"/>
@@ -1797,20 +1678,13 @@
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
 Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
+61% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="F10" s="7" t="n"/>
@@ -1826,20 +1700,13 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-18% pred | 18% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E11" s="7" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-40% pred | 40% hist
-[INCLUDE]</t>
+          <t>FIT
+Mrigakshi Jaiswal
+65% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
@@ -1854,28 +1721,35 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
+          <t>Barre 57
+Pranjali Jain
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Anisha Shah
-18% pred | 18% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
+Simran Dutt
+35% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-57% pred | 57% hist
-[PROTECT_EXACT]</t>
+62% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H12" s="7" t="n"/>
@@ -1887,31 +1761,38 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-54% pred | 54% hist
-[INCLUDE]</t>
+45% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-75% pred | 75% hist
-[PINNED]</t>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Rohan Dahima
-43% pred | 43% hist
-[PINNED]</t>
+45% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
@@ -1926,25 +1807,25 @@
         <is>
           <t>Mat 57
 Anisha Shah
-65% pred | 65% hist
-[PINNED]</t>
+65% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
-20% pred | 20% hist
-[CONSIDER]</t>
+0% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
+61% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
@@ -1960,13 +1841,20 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
@@ -1981,155 +1869,225 @@
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+          <t>FIT
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-73% pred | 73% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-52% pred | 52% hist
-[PROTECT]</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+40% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>12:15</t>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Anmol Sharma
+71% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
+          <t>Barre 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
+Anisha Shah
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Karan Bhatia
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Richard D'Costa
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Simran Dutt
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Bret Saldanha
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -2138,51 +2096,37 @@
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-41% pred | 41% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simran Dutt
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-44% pred | 44% hist
-[PINNED]</t>
+[]</t>
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -2191,233 +2135,79 @@
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Anisha Shah
-40% pred | 40% hist
-[PROTECT_EXACT]</t>
+28% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Simran Dutt
-29% pred | 29% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+          <t>Barre 57
+Raunak Khemuka
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Anmol Sharma
+          <t>Cardio Barre
+Siddhartha Kusuma
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Mrigakshi Jaiswal
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simonelle De Vitre
-34% pred | 34% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Karan Bhatia
-26% pred | 26% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-44% pred | 44% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-26% pred | 26% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simran Dutt
-83% pred | 83% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-39% pred | 39% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-62% pred | 62% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-22% pred | 22% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2433,7 +2223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2512,16 +2302,16 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-70% pred | 70% hist
-[PINNED]</t>
+75% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Pranjali Jain
-13% pred | 13% hist
-[CONSIDER]</t>
+18% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D3" s="7" t="n"/>
@@ -2536,46 +2326,32 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-43% pred | 43% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
-82% pred | 82% hist
-[PINNED]</t>
+82% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Strength Lab
 Anisha Shah
-66% pred | 66% hist
-[PINNED]</t>
+70% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
-89% pred | 89% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Mrigakshi Jaiswal
-32% pred | 32% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+89% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
@@ -2588,9 +2364,9 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-32% pred | 32% hist
-[CONSIDER]</t>
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -2598,8 +2374,8 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-87% pred | 87% hist
-[PINNED]</t>
+84% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -2607,8 +2383,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 33% hist
-[INCLUDE]</t>
+33% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
@@ -2620,25 +2396,25 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-90% pred | 90% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n"/>
+90% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simran Dutt
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
     </row>
@@ -2652,28 +2428,21 @@
         <is>
           <t>Mat 57
 Atulan Purohit
-57% pred | 57% hist
-[PINNED]</t>
+57% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-40% pred | 40% hist
-[INCLUDE]</t>
+40% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
@@ -2689,13 +2458,20 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-69% pred | 69% hist
-[PROTECT_EXACT]</t>
+68% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
@@ -2708,8 +2484,8 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 64% hist
-[CONSIDER]</t>
+60% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -2717,18 +2493,18 @@
         <is>
           <t>Back Body Blaze
 Anisha Shah
-60% pred | 60% hist
-[PINNED]</t>
+60% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
 Rohan Dahima
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
+63% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H9" s="7" t="n"/>
@@ -2741,20 +2517,13 @@
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
 Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
+61% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="F10" s="7" t="n"/>
@@ -2770,20 +2539,13 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-18% pred | 18% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E11" s="7" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-40% pred | 40% hist
-[INCLUDE]</t>
+          <t>FIT
+Mrigakshi Jaiswal
+65% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
@@ -2798,28 +2560,35 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
+          <t>Barre 57
+Pranjali Jain
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Anisha Shah
-18% pred | 18% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
+Simran Dutt
+35% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-57% pred | 57% hist
-[PROTECT_EXACT]</t>
+62% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H12" s="7" t="n"/>
@@ -2831,31 +2600,38 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-54% pred | 54% hist
-[INCLUDE]</t>
+45% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-75% pred | 75% hist
-[PINNED]</t>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Rohan Dahima
-43% pred | 43% hist
-[PINNED]</t>
+45% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
@@ -2870,25 +2646,25 @@
         <is>
           <t>Mat 57
 Anisha Shah
-65% pred | 65% hist
-[PINNED]</t>
+65% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
-20% pred | 20% hist
-[CONSIDER]</t>
+0% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
+61% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
@@ -2904,13 +2680,20 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
@@ -2925,155 +2708,225 @@
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+          <t>FIT
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-73% pred | 73% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n"/>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-52% pred | 52% hist
-[PROTECT]</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+40% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>12:15</t>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Anmol Sharma
+71% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
+          <t>Barre 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
+Anisha Shah
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Karan Bhatia
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Richard D'Costa
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Simran Dutt
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Bret Saldanha
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -3082,51 +2935,37 @@
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-41% pred | 41% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simran Dutt
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-44% pred | 44% hist
-[PINNED]</t>
+[]</t>
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -3135,233 +2974,79 @@
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Anisha Shah
-40% pred | 40% hist
-[PROTECT_EXACT]</t>
+28% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Simran Dutt
-29% pred | 29% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+          <t>Barre 57
+Raunak Khemuka
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Anmol Sharma
+          <t>Cardio Barre
+Siddhartha Kusuma
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Mrigakshi Jaiswal
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simonelle De Vitre
-34% pred | 34% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Karan Bhatia
-26% pred | 26% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-44% pred | 44% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-26% pred | 26% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simran Dutt
-83% pred | 83% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-39% pred | 39% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-62% pred | 62% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-22% pred | 22% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -624,15 +624,15 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-75% pred | 0% hist
+70% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Pranjali Jain
-18% pred | 0% hist
+13% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -661,7 +661,7 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-70% pred | 0% hist
+66% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -696,7 +696,7 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-84% pred | 0% hist
+87% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -733,7 +733,7 @@
         <is>
           <t>PowerCycle
 Simran Dutt
-43% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -765,7 +765,14 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -780,7 +787,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -789,7 +796,7 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
+Karanvir Bhatia
 24% pred | 0% hist
 []</t>
         </is>
@@ -806,7 +813,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-60% pred | 0% hist
+64% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -848,7 +855,14 @@
 []</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
@@ -882,9 +896,9 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
-26% pred | 0% hist
+          <t>Cardio Barre Express
+Anisha Shah
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -900,8 +914,8 @@
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Simran Dutt
-35% pred | 0% hist
+Raunak Khemuka
+32% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -909,7 +923,7 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-62% pred | 0% hist
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -922,23 +936,23 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -952,7 +966,7 @@
         <is>
           <t>Cardio Barre
 Rohan Dahima
-45% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -973,11 +987,11 @@
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-0% pred | 0% hist
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+38% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -985,7 +999,7 @@
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-61% pred | 0% hist
+56% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1002,20 +1016,13 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>FIT
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
@@ -1028,21 +1035,14 @@
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-76% pred | 0% hist
+72% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1078,7 +1078,7 @@
         <is>
           <t>Mat 57
 Bret Saldanha
-40% pred | 0% hist
+41% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1126,14 +1126,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anmol Sharma
-71% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
@@ -1168,19 +1161,12 @@
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
 Karan Bhatia
-86% pred | 0% hist
+82% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1192,7 +1178,14 @@
 []</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
@@ -1206,7 +1199,7 @@
       <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Richard D'Costa
+Simonelle De Vitre
 26% pred | 0% hist
 []</t>
         </is>
@@ -1220,11 +1213,11 @@
         </is>
       </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-34% pred | 0% hist
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1252,17 +1245,17 @@
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anmol Sharma
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
@@ -1276,15 +1269,15 @@
         <is>
           <t>PowerCycle
 Simran Dutt
-85% pred | 0% hist
+83% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
@@ -1318,8 +1311,8 @@
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
+Richard D'Costa
+39% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1327,7 +1320,7 @@
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
-69% pred | 0% hist
+62% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1335,40 +1328,19 @@
         <is>
           <t>PowerCycle Express
 Karan Bhatia
-50% pred | 0% hist
+42% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1384,7 +1356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1463,15 +1435,15 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-75% pred | 0% hist
+70% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Pranjali Jain
-18% pred | 0% hist
+13% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1500,7 +1472,7 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-70% pred | 0% hist
+66% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1535,7 +1507,7 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-84% pred | 0% hist
+87% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1572,7 +1544,7 @@
         <is>
           <t>PowerCycle
 Simran Dutt
-43% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1604,7 +1576,14 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -1619,7 +1598,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1628,7 +1607,7 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
+Karanvir Bhatia
 24% pred | 0% hist
 []</t>
         </is>
@@ -1645,7 +1624,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-60% pred | 0% hist
+64% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1687,7 +1666,14 @@
 []</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
@@ -1721,9 +1707,9 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
-26% pred | 0% hist
+          <t>Cardio Barre Express
+Anisha Shah
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1739,8 +1725,8 @@
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Simran Dutt
-35% pred | 0% hist
+Raunak Khemuka
+32% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1748,7 +1734,7 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-62% pred | 0% hist
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1761,23 +1747,23 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -1791,7 +1777,7 @@
         <is>
           <t>Cardio Barre
 Rohan Dahima
-45% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1812,11 +1798,11 @@
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-0% pred | 0% hist
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+38% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1824,7 +1810,7 @@
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-61% pred | 0% hist
+56% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1841,20 +1827,13 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>FIT
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
@@ -1867,21 +1846,14 @@
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-76% pred | 0% hist
+72% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1917,7 +1889,7 @@
         <is>
           <t>Mat 57
 Bret Saldanha
-40% pred | 0% hist
+41% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1965,14 +1937,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anmol Sharma
-71% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
@@ -2007,19 +1972,12 @@
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
 Karan Bhatia
-86% pred | 0% hist
+82% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2031,7 +1989,14 @@
 []</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
@@ -2045,7 +2010,7 @@
       <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Richard D'Costa
+Simonelle De Vitre
 26% pred | 0% hist
 []</t>
         </is>
@@ -2059,11 +2024,11 @@
         </is>
       </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-34% pred | 0% hist
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2091,17 +2056,17 @@
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anmol Sharma
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
@@ -2115,15 +2080,15 @@
         <is>
           <t>PowerCycle
 Simran Dutt
-85% pred | 0% hist
+83% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
@@ -2157,8 +2122,8 @@
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
+Richard D'Costa
+39% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2166,7 +2131,7 @@
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
-69% pred | 0% hist
+62% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2174,40 +2139,19 @@
         <is>
           <t>PowerCycle Express
 Karan Bhatia
-50% pred | 0% hist
+42% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2223,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2302,15 +2246,15 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-75% pred | 0% hist
+70% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Pranjali Jain
-18% pred | 0% hist
+13% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2339,7 +2283,7 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-70% pred | 0% hist
+66% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2374,7 +2318,7 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-84% pred | 0% hist
+87% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2411,7 +2355,7 @@
         <is>
           <t>PowerCycle
 Simran Dutt
-43% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2443,7 +2387,14 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2458,7 +2409,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2467,7 +2418,7 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
+Karanvir Bhatia
 24% pred | 0% hist
 []</t>
         </is>
@@ -2484,7 +2435,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-60% pred | 0% hist
+64% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2526,7 +2477,14 @@
 []</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
@@ -2560,9 +2518,9 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
-26% pred | 0% hist
+          <t>Cardio Barre Express
+Anisha Shah
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2578,8 +2536,8 @@
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Simran Dutt
-35% pred | 0% hist
+Raunak Khemuka
+32% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2587,7 +2545,7 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-62% pred | 0% hist
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2600,23 +2558,23 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -2630,7 +2588,7 @@
         <is>
           <t>Cardio Barre
 Rohan Dahima
-45% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2651,11 +2609,11 @@
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-0% pred | 0% hist
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+38% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2663,7 +2621,7 @@
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-61% pred | 0% hist
+56% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2680,20 +2638,13 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>FIT
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
@@ -2706,21 +2657,14 @@
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-76% pred | 0% hist
+72% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2756,7 +2700,7 @@
         <is>
           <t>Mat 57
 Bret Saldanha
-40% pred | 0% hist
+41% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2804,14 +2748,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anmol Sharma
-71% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
@@ -2846,19 +2783,12 @@
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
 Karan Bhatia
-86% pred | 0% hist
+82% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2870,7 +2800,14 @@
 []</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
@@ -2884,7 +2821,7 @@
       <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Richard D'Costa
+Simonelle De Vitre
 26% pred | 0% hist
 []</t>
         </is>
@@ -2898,11 +2835,11 @@
         </is>
       </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-34% pred | 0% hist
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2930,17 +2867,17 @@
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anmol Sharma
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
@@ -2954,15 +2891,15 @@
         <is>
           <t>PowerCycle
 Simran Dutt
-85% pred | 0% hist
+83% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
@@ -2996,8 +2933,8 @@
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
+Richard D'Costa
+39% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3005,7 +2942,7 @@
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
-69% pred | 0% hist
+62% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3013,40 +2950,19 @@
         <is>
           <t>PowerCycle Express
 Karan Bhatia
-50% pred | 0% hist
+42% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -51,10 +51,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
@@ -62,6 +58,10 @@
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="00374151"/>
@@ -102,17 +102,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,10 +172,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -624,15 +624,15 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-70% pred | 0% hist
+0% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Pranjali Jain
-13% pred | 0% hist
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -648,7 +648,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -661,20 +668,27 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
-89% pred | 0% hist
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+62% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -683,7 +697,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Bret Saldanha
@@ -692,11 +706,11 @@
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-87% pred | 0% hist
+83% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -718,10 +732,17 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -729,11 +750,11 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
-40% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -741,12 +762,12 @@
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -765,7 +786,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -787,7 +808,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-69% pred | 0% hist
+71% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -804,7 +825,7 @@
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -813,7 +834,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 0% hist
+60% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -851,7 +872,7 @@
         <is>
           <t>Strength Lab (Push)
 Vivaran Dhasmana
-61% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -867,7 +888,7 @@
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -875,7 +896,14 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -896,9 +924,9 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Anisha Shah
-18% pred | 0% hist
+          <t>Barre 57
+Pranjali Jain
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -911,15 +939,68 @@
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -927,58 +1008,26 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Rohan Dahima
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="inlineStr">
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -986,35 +1035,63 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>FIT
-Raunak Khemuka
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+Rohan Dahima
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -1022,31 +1099,17 @@
 []</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-72% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1055,45 +1118,87 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Bret Saldanha
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1101,16 +1206,16 @@
 []</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -1118,7 +1223,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -1126,33 +1231,40 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Anmol Sharma
+74% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1160,17 +1272,17 @@
 []</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -1178,33 +1290,26 @@
 []</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Simonelle De Vitre
+Richard D'Costa
 26% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -1212,31 +1317,24 @@
 []</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1244,38 +1342,31 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anmol Sharma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
-83% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1283,16 +1374,16 @@
 []</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -1300,7 +1391,7 @@
 []</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Raunak Khemuka
@@ -1308,39 +1399,60 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
 42% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1356,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1435,15 +1547,15 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-70% pred | 0% hist
+0% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Pranjali Jain
-13% pred | 0% hist
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1459,7 +1571,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1472,20 +1591,27 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
-89% pred | 0% hist
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+62% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -1494,7 +1620,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Bret Saldanha
@@ -1503,11 +1629,11 @@
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-87% pred | 0% hist
+83% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1529,10 +1655,17 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1540,11 +1673,11 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
-40% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1552,12 +1685,12 @@
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -1576,7 +1709,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1598,7 +1731,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-69% pred | 0% hist
+71% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1615,7 +1748,7 @@
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1624,7 +1757,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 0% hist
+60% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1662,7 +1795,7 @@
         <is>
           <t>Strength Lab (Push)
 Vivaran Dhasmana
-61% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1678,7 +1811,7 @@
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -1686,7 +1819,14 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1707,9 +1847,9 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Anisha Shah
-18% pred | 0% hist
+          <t>Barre 57
+Pranjali Jain
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1722,15 +1862,68 @@
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1738,58 +1931,26 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Rohan Dahima
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="inlineStr">
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1797,35 +1958,63 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>FIT
-Raunak Khemuka
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+Rohan Dahima
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -1833,31 +2022,17 @@
 []</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-72% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1866,45 +2041,87 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Bret Saldanha
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1912,16 +2129,16 @@
 []</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -1929,7 +2146,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -1937,33 +2154,40 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Anmol Sharma
+74% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1971,17 +2195,17 @@
 []</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -1989,33 +2213,26 @@
 []</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Simonelle De Vitre
+Richard D'Costa
 26% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -2023,31 +2240,24 @@
 []</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2055,38 +2265,31 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anmol Sharma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
-83% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2094,16 +2297,16 @@
 []</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -2111,7 +2314,7 @@
 []</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Raunak Khemuka
@@ -2119,39 +2322,60 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
 42% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2167,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2246,15 +2470,15 @@
         <is>
           <t>Strength Lab
 Reshma Sharma
-70% pred | 0% hist
+0% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Pranjali Jain
-13% pred | 0% hist
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2270,7 +2494,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -2283,20 +2514,27 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
-89% pred | 0% hist
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+62% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -2305,7 +2543,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Bret Saldanha
@@ -2314,11 +2552,11 @@
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-87% pred | 0% hist
+83% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2340,10 +2578,17 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2351,11 +2596,11 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
-40% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2363,12 +2608,12 @@
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -2387,7 +2632,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2409,7 +2654,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-69% pred | 0% hist
+71% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2426,7 +2671,7 @@
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -2435,7 +2680,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 0% hist
+60% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2473,7 +2718,7 @@
         <is>
           <t>Strength Lab (Push)
 Vivaran Dhasmana
-61% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2489,7 +2734,7 @@
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2497,7 +2742,14 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -2518,9 +2770,9 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Anisha Shah
-18% pred | 0% hist
+          <t>Barre 57
+Pranjali Jain
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2533,15 +2785,68 @@
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2549,58 +2854,26 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Rohan Dahima
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="inlineStr">
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2608,35 +2881,63 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>FIT
-Raunak Khemuka
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+Rohan Dahima
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -2644,31 +2945,17 @@
 []</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-72% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2677,45 +2964,87 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Bret Saldanha
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2723,16 +3052,16 @@
 []</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -2740,7 +3069,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -2748,33 +3077,40 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Anmol Sharma
+74% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -2782,17 +3118,17 @@
 []</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -2800,33 +3136,26 @@
 []</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Simonelle De Vitre
+Richard D'Costa
 26% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -2834,31 +3163,24 @@
 []</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2866,38 +3188,31 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anmol Sharma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
-83% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2905,16 +3220,16 @@
 []</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -2922,7 +3237,7 @@
 []</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Raunak Khemuka
@@ -2930,39 +3245,60 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
 42% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -51,6 +51,10 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
@@ -58,10 +62,6 @@
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00374151"/>
@@ -102,17 +102,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,10 +172,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -648,14 +648,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -672,11 +665,11 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-62% pred | 0% hist
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Rohan Dahima
+89% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -697,7 +690,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Bret Saldanha
@@ -706,7 +699,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -742,7 +735,7 @@
       </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -750,7 +743,7 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
@@ -762,12 +755,12 @@
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -786,7 +779,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -825,7 +818,7 @@
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -888,7 +881,7 @@
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -896,7 +889,7 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Raunak Khemuka
@@ -922,11 +915,11 @@
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-27% pred | 0% hist
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+44% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -939,7 +932,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -947,35 +940,21 @@
 []</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1000,7 +979,7 @@
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1014,20 +993,20 @@
       <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Cardio Barre Express
 Reshma Sharma
 10% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1048,7 +1027,7 @@
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-60% pred | 0% hist
+63% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1084,7 +1063,7 @@
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -1105,7 +1084,7 @@
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-76% pred | 0% hist
+79% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1121,7 +1100,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
@@ -1130,49 +1109,7 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Bret Saldanha
@@ -1181,24 +1118,17 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1206,16 +1136,16 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -1223,7 +1153,7 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -1231,7 +1161,7 @@
 []</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Anmol Sharma
@@ -1239,7 +1169,7 @@
 []</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -1247,24 +1177,24 @@
 []</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1272,8 +1202,8 @@
 []</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -1281,8 +1211,8 @@
 []</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -1290,18 +1220,25 @@
 []</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Bret Saldanha
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Richard D'Costa
@@ -1309,7 +1246,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -1317,24 +1254,31 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1342,21 +1286,21 @@
 []</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
@@ -1364,9 +1308,9 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1374,16 +1318,16 @@
 []</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -1391,7 +1335,7 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Raunak Khemuka
@@ -1399,7 +1343,7 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -1407,7 +1351,7 @@
 []</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -1415,7 +1359,7 @@
 []</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
@@ -1423,25 +1367,25 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1449,10 +1393,10 @@
 []</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1468,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1571,14 +1515,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1595,11 +1532,11 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-62% pred | 0% hist
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Rohan Dahima
+89% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1620,7 +1557,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Bret Saldanha
@@ -1629,7 +1566,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1665,7 +1602,7 @@
       </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1673,7 +1610,7 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
@@ -1685,12 +1622,12 @@
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -1709,7 +1646,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1748,7 +1685,7 @@
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1811,7 +1748,7 @@
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -1819,7 +1756,7 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Raunak Khemuka
@@ -1845,11 +1782,11 @@
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-27% pred | 0% hist
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+44% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1862,7 +1799,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -1870,35 +1807,21 @@
 []</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1923,7 +1846,7 @@
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1937,20 +1860,20 @@
       <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Cardio Barre Express
 Reshma Sharma
 10% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1971,7 +1894,7 @@
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-60% pred | 0% hist
+63% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2007,7 +1930,7 @@
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -2028,7 +1951,7 @@
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-76% pred | 0% hist
+79% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2044,7 +1967,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
@@ -2053,49 +1976,7 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Bret Saldanha
@@ -2104,24 +1985,17 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2129,16 +2003,16 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -2146,7 +2020,7 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -2154,7 +2028,7 @@
 []</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Anmol Sharma
@@ -2162,7 +2036,7 @@
 []</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -2170,24 +2044,24 @@
 []</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -2195,8 +2069,8 @@
 []</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -2204,8 +2078,8 @@
 []</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -2213,18 +2087,25 @@
 []</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Bret Saldanha
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Richard D'Costa
@@ -2232,7 +2113,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -2240,24 +2121,31 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2265,21 +2153,21 @@
 []</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
@@ -2287,9 +2175,9 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2297,16 +2185,16 @@
 []</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -2314,7 +2202,7 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Raunak Khemuka
@@ -2322,7 +2210,7 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -2330,7 +2218,7 @@
 []</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -2338,7 +2226,7 @@
 []</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
@@ -2346,25 +2234,25 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2372,10 +2260,10 @@
 []</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2391,7 +2279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2494,14 +2382,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -2518,11 +2399,11 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-62% pred | 0% hist
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Rohan Dahima
+89% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2543,7 +2424,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Bret Saldanha
@@ -2552,7 +2433,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2588,7 +2469,7 @@
       </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2596,7 +2477,7 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
@@ -2608,12 +2489,12 @@
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -2632,7 +2513,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2671,7 +2552,7 @@
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -2734,7 +2615,7 @@
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2742,7 +2623,7 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Raunak Khemuka
@@ -2768,11 +2649,11 @@
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-27% pred | 0% hist
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+44% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2785,7 +2666,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -2793,35 +2674,21 @@
 []</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -2846,7 +2713,7 @@
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2860,20 +2727,20 @@
       <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Cardio Barre Express
 Reshma Sharma
 10% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2894,7 +2761,7 @@
         <is>
           <t>Strength Lab (Full Body)
 Mrigakshi Jaiswal
-60% pred | 0% hist
+63% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2930,7 +2797,7 @@
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -2951,7 +2818,7 @@
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
-76% pred | 0% hist
+79% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2967,7 +2834,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
@@ -2976,49 +2843,7 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Bret Saldanha
@@ -3027,24 +2852,17 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -3052,16 +2870,16 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -3069,7 +2887,7 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -3077,7 +2895,7 @@
 []</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Anmol Sharma
@@ -3085,7 +2903,7 @@
 []</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -3093,24 +2911,24 @@
 []</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -3118,8 +2936,8 @@
 []</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -3127,8 +2945,8 @@
 []</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -3136,18 +2954,25 @@
 []</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Bret Saldanha
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Richard D'Costa
@@ -3155,7 +2980,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -3163,24 +2988,31 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -3188,21 +3020,21 @@
 []</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Simran Dutt
@@ -3210,9 +3042,9 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -3220,16 +3052,16 @@
 []</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -3237,7 +3069,7 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Raunak Khemuka
@@ -3245,7 +3077,7 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -3253,7 +3085,7 @@
 []</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -3261,7 +3093,7 @@
 []</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
@@ -3269,25 +3101,25 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -3295,10 +3127,10 @@
 []</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -648,7 +648,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -998,14 +1005,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Reshma Sharma
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1103,7 +1103,14 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
@@ -1124,7 +1131,14 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
@@ -1370,7 +1384,7 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
@@ -1515,7 +1529,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1865,14 +1886,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Reshma Sharma
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1970,7 +1984,14 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
@@ -1991,7 +2012,14 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
@@ -2237,7 +2265,7 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
@@ -2382,7 +2410,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -2732,14 +2767,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Reshma Sharma
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2837,7 +2865,14 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
@@ -2858,7 +2893,14 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
@@ -3104,7 +3146,7 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Siddhartha Kusuma
 20% pred | 0% hist
 []</t>

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -648,14 +648,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -681,14 +674,7 @@
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -700,7 +686,7 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Bret Saldanha
+Raunak Khemuka
 32% pred | 0% hist
 []</t>
         </is>
@@ -732,14 +718,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="9" t="inlineStr">
@@ -753,7 +732,7 @@
       <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Simran Dutt
+Raunak Khemuka
 43% pred | 0% hist
 []</t>
         </is>
@@ -786,14 +765,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -817,7 +789,7 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
+Cauveri Vikrant
 24% pred | 0% hist
 []</t>
         </is>
@@ -899,7 +871,7 @@
       <c r="E11" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Raunak Khemuka
+Simran Dutt
 36% pred | 0% hist
 []</t>
         </is>
@@ -922,11 +894,11 @@
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-44% pred | 0% hist
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -947,7 +919,14 @@
 []</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -957,7 +936,14 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
@@ -1100,23 +1086,65 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Bret Saldanha
@@ -1125,24 +1153,17 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1150,16 +1171,16 @@
 []</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -1167,15 +1188,15 @@
 []</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Raunak Khemuka
+Simran Dutt
 29% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Anmol Sharma
@@ -1183,7 +1204,7 @@
 []</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -1191,24 +1212,24 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1216,8 +1237,8 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -1225,8 +1246,8 @@
 []</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -1234,25 +1255,25 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Bret Saldanha
+Vivaran Dhasmana
 37% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Richard D'Costa
@@ -1260,39 +1281,132 @@
 []</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Simran Dutt
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1300,117 +1414,10 @@
 []</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simran Dutt
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-51% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1426,7 +1433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1529,14 +1536,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1562,14 +1562,7 @@
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -1581,7 +1574,7 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Bret Saldanha
+Raunak Khemuka
 32% pred | 0% hist
 []</t>
         </is>
@@ -1613,14 +1606,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="9" t="inlineStr">
@@ -1634,7 +1620,7 @@
       <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Simran Dutt
+Raunak Khemuka
 43% pred | 0% hist
 []</t>
         </is>
@@ -1667,14 +1653,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -1698,7 +1677,7 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
+Cauveri Vikrant
 24% pred | 0% hist
 []</t>
         </is>
@@ -1780,7 +1759,7 @@
       <c r="E11" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Raunak Khemuka
+Simran Dutt
 36% pred | 0% hist
 []</t>
         </is>
@@ -1803,11 +1782,11 @@
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-44% pred | 0% hist
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1828,7 +1807,14 @@
 []</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -1838,7 +1824,14 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
@@ -1981,23 +1974,65 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Bret Saldanha
@@ -2006,24 +2041,17 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2031,16 +2059,16 @@
 []</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -2048,15 +2076,15 @@
 []</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Raunak Khemuka
+Simran Dutt
 29% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Anmol Sharma
@@ -2064,7 +2092,7 @@
 []</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -2072,24 +2100,24 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -2097,8 +2125,8 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -2106,8 +2134,8 @@
 []</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -2115,25 +2143,25 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Bret Saldanha
+Vivaran Dhasmana
 37% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Richard D'Costa
@@ -2141,39 +2169,132 @@
 []</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Simran Dutt
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2181,117 +2302,10 @@
 []</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simran Dutt
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-51% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2307,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2410,14 +2424,7 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -2443,14 +2450,7 @@
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -2462,7 +2462,7 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Bret Saldanha
+Raunak Khemuka
 32% pred | 0% hist
 []</t>
         </is>
@@ -2494,14 +2494,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="9" t="inlineStr">
@@ -2515,7 +2508,7 @@
       <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Simran Dutt
+Raunak Khemuka
 43% pred | 0% hist
 []</t>
         </is>
@@ -2548,14 +2541,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2579,7 +2565,7 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
+Cauveri Vikrant
 24% pred | 0% hist
 []</t>
         </is>
@@ -2661,7 +2647,7 @@
       <c r="E11" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Raunak Khemuka
+Simran Dutt
 36% pred | 0% hist
 []</t>
         </is>
@@ -2684,11 +2670,11 @@
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-44% pred | 0% hist
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2709,7 +2695,14 @@
 []</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -2719,7 +2712,14 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
@@ -2862,23 +2862,65 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Bret Saldanha
@@ -2887,24 +2929,17 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2912,16 +2947,16 @@
 []</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -2929,15 +2964,15 @@
 []</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Raunak Khemuka
+Simran Dutt
 29% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Anmol Sharma
@@ -2945,7 +2980,7 @@
 []</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -2953,24 +2988,24 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -2978,8 +3013,8 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -2987,8 +3022,8 @@
 []</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Karan Bhatia
@@ -2996,25 +3031,25 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Bret Saldanha
+Vivaran Dhasmana
 37% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Richard D'Costa
@@ -3022,39 +3057,132 @@
 []</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Simran Dutt
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -3062,117 +3190,10 @@
 []</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simran Dutt
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-51% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -92,12 +92,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -164,10 +164,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -628,19 +628,26 @@
 []</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+21% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -648,8 +655,15 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -673,9 +687,16 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -685,13 +706,13 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n"/>
+          <t>PowerCycle
+Vivaran Dhasmana
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
       <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -700,17 +721,10 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -718,27 +732,41 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Rohan Dahima
-90% pred | 0% hist
+Mrigakshi Jaiswal
+73% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Raunak Khemuka
+Karanvir Bhatia
 43% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -754,19 +782,33 @@
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Pranjali Jain
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -774,8 +816,15 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -784,17 +833,10 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -805,13 +847,13 @@
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
-Richard D'Costa
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
+Vivaran Dhasmana
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Anisha Shah
@@ -819,17 +861,24 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -837,27 +886,34 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Reshma Sharma
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -865,18 +921,11 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simran Dutt
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -884,8 +933,8 @@
 []</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -893,41 +942,34 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -935,27 +977,41 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Rohan Dahima
@@ -970,8 +1026,8 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -980,10 +1036,17 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -991,7 +1054,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="6" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1000,15 +1063,8 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -1017,8 +1073,8 @@
 []</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1026,9 +1082,16 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1036,17 +1099,24 @@
 []</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -1054,18 +1124,25 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FIT
+Reshma Sharma
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
 Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -1074,7 +1151,7 @@
 []</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1086,41 +1163,48 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Bret Saldanha
-20% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1131,23 +1215,23 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
 28% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Bret Saldanha
+Anmol Sharma
 41% pred | 0% hist
 []</t>
         </is>
@@ -1159,11 +1243,11 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1171,8 +1255,8 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
@@ -1180,48 +1264,34 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simran Dutt
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Karan Bhatia
 29% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anmol Sharma
-74% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-86% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -1229,41 +1299,41 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>FIT
-Anisha Shah
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
+Karanvir Bhatia
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Karan Bhatia
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Vivaran Dhasmana
 37% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1271,17 +1341,10 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Richard D'Costa
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -1289,16 +1352,9 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1309,17 +1365,17 @@
       <c r="B25" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Bret Saldanha
+Raunak Khemuka
 42% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -1327,27 +1383,27 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -1363,61 +1419,47 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
+Raunak Khemuka
 51% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1516,19 +1558,26 @@
 []</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+21% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1536,8 +1585,15 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1561,9 +1617,16 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1573,13 +1636,13 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n"/>
+          <t>PowerCycle
+Vivaran Dhasmana
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
       <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1588,17 +1651,10 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1606,27 +1662,41 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Rohan Dahima
-90% pred | 0% hist
+Mrigakshi Jaiswal
+73% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Raunak Khemuka
+Karanvir Bhatia
 43% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -1642,19 +1712,33 @@
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Pranjali Jain
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1662,8 +1746,15 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -1672,17 +1763,10 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -1693,13 +1777,13 @@
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
-Richard D'Costa
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
+Vivaran Dhasmana
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Anisha Shah
@@ -1707,17 +1791,24 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1725,27 +1816,34 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Reshma Sharma
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -1753,18 +1851,11 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simran Dutt
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -1772,8 +1863,8 @@
 []</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1781,41 +1872,34 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -1823,27 +1907,41 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Rohan Dahima
@@ -1858,8 +1956,8 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1868,10 +1966,17 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -1879,7 +1984,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="6" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1888,15 +1993,8 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -1905,8 +2003,8 @@
 []</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1914,9 +2012,16 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1924,17 +2029,24 @@
 []</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -1942,18 +2054,25 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FIT
+Reshma Sharma
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
 Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -1962,7 +2081,7 @@
 []</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1974,41 +2093,48 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Bret Saldanha
-20% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2019,23 +2145,23 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
 28% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Bret Saldanha
+Anmol Sharma
 41% pred | 0% hist
 []</t>
         </is>
@@ -2047,11 +2173,11 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2059,8 +2185,8 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
@@ -2068,48 +2194,34 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simran Dutt
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Karan Bhatia
 29% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anmol Sharma
-74% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-86% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -2117,41 +2229,41 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>FIT
-Anisha Shah
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
+Karanvir Bhatia
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Karan Bhatia
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Vivaran Dhasmana
 37% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -2159,17 +2271,10 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Richard D'Costa
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -2177,16 +2282,9 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -2197,17 +2295,17 @@
       <c r="B25" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Bret Saldanha
+Raunak Khemuka
 42% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -2215,27 +2313,27 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -2251,61 +2349,47 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
+Raunak Khemuka
 51% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2404,19 +2488,26 @@
 []</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+21% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -2424,8 +2515,15 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -2449,9 +2547,16 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2461,13 +2566,13 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n"/>
+          <t>PowerCycle
+Vivaran Dhasmana
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
       <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2476,17 +2581,10 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -2494,27 +2592,41 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Rohan Dahima
-90% pred | 0% hist
+Mrigakshi Jaiswal
+73% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Raunak Khemuka
+Karanvir Bhatia
 43% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -2530,19 +2642,33 @@
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Pranjali Jain
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2550,8 +2676,15 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -2560,17 +2693,10 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -2581,13 +2707,13 @@
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
-Richard D'Costa
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
+Vivaran Dhasmana
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Anisha Shah
@@ -2595,17 +2721,24 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Mrigakshi Jaiswal
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -2613,27 +2746,34 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Reshma Sharma
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -2641,18 +2781,11 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simran Dutt
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -2660,8 +2793,8 @@
 []</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -2669,41 +2802,34 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -2711,27 +2837,41 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Rohan Dahima
@@ -2746,8 +2886,8 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2756,10 +2896,17 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -2767,7 +2914,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="6" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2776,15 +2923,8 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -2793,8 +2933,8 @@
 []</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2802,9 +2942,16 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2812,17 +2959,24 @@
 []</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -2830,18 +2984,25 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FIT
+Reshma Sharma
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
 Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -2850,7 +3011,7 @@
 []</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2862,41 +3023,48 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Bret Saldanha
-20% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2907,23 +3075,23 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
 28% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Bret Saldanha
+Anmol Sharma
 41% pred | 0% hist
 []</t>
         </is>
@@ -2935,11 +3103,11 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2947,8 +3115,8 @@
 []</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
@@ -2956,48 +3124,34 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simran Dutt
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Karan Bhatia
 29% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anmol Sharma
-74% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-86% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -3005,41 +3159,41 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>FIT
-Anisha Shah
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
+Karanvir Bhatia
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Karan Bhatia
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Vivaran Dhasmana
 37% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -3047,17 +3201,10 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Richard D'Costa
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Raunak Khemuka
@@ -3065,16 +3212,9 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -3085,17 +3225,17 @@
       <c r="B25" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
-Bret Saldanha
+Raunak Khemuka
 42% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -3103,27 +3243,27 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -3139,61 +3279,47 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
+Raunak Khemuka
 51% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,11 +64,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00374151"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +121,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F0F0F5"/>
       </patternFill>
     </fill>
@@ -147,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -178,6 +187,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -545,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -631,8 +643,22 @@
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -641,7 +667,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -667,7 +700,14 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -679,12 +719,19 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Anisha Shah
+Bret Saldanha
 32% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -693,16 +740,7 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -710,6 +748,8 @@
 []</t>
         </is>
       </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -718,33 +758,40 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -773,13 +820,20 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -789,14 +843,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -816,14 +863,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -833,13 +873,20 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Rohan Dahima
-63% pred | 0% hist
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -852,20 +899,27 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
+Vivaran Dhasmana
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Rohan Dahima
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-69% pred | 0% hist
+38% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -880,14 +934,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="7" t="inlineStr">
@@ -907,25 +954,32 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Reshma Sharma
+Anisha Shah
 44% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
     </row>
@@ -935,15 +989,15 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
@@ -956,9 +1010,9 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Reshma Sharma
-63% pred | 0% hist
+          <t>PowerCycle
+Rohan Dahima
+90% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -987,7 +1041,14 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
@@ -998,7 +1059,14 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1008,7 +1076,14 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -1039,14 +1114,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -1055,7 +1123,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -1069,48 +1144,43 @@
       <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
-Atulan Purohit
+Reshma Sharma
 79% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1118,16 +1188,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
@@ -1135,30 +1196,37 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -1167,100 +1235,100 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-31% pred | 0% hist
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+67% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Karan Bhatia
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Karanvir Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
@@ -1268,42 +1336,56 @@
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1311,33 +1393,40 @@
 []</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Pranjali Jain
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
+Reshma Sharma
 52% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -1345,58 +1434,9 @@
 []</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-51% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Raunak Khemuka
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1412,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1498,8 +1538,22 @@
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -1508,7 +1562,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -1534,7 +1595,14 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -1546,12 +1614,19 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Anisha Shah
+Bret Saldanha
 32% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1560,16 +1635,7 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1577,6 +1643,8 @@
 []</t>
         </is>
       </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1585,33 +1653,40 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -1640,13 +1715,20 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -1656,14 +1738,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -1683,14 +1758,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1700,13 +1768,20 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Rohan Dahima
-63% pred | 0% hist
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1719,20 +1794,27 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
+Vivaran Dhasmana
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Rohan Dahima
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-69% pred | 0% hist
+38% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1747,14 +1829,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="7" t="inlineStr">
@@ -1774,25 +1849,32 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Reshma Sharma
+Anisha Shah
 44% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
     </row>
@@ -1802,15 +1884,15 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
@@ -1823,9 +1905,9 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Reshma Sharma
-63% pred | 0% hist
+          <t>PowerCycle
+Rohan Dahima
+90% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1854,7 +1936,14 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
@@ -1865,7 +1954,14 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1875,7 +1971,14 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -1906,14 +2009,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -1922,7 +2018,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -1936,48 +2039,43 @@
       <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
-Atulan Purohit
+Reshma Sharma
 79% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1985,16 +2083,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
@@ -2002,30 +2091,37 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -2034,100 +2130,100 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-31% pred | 0% hist
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+67% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Karan Bhatia
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Karanvir Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
@@ -2135,42 +2231,56 @@
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2178,33 +2288,40 @@
 []</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Pranjali Jain
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
+Reshma Sharma
 52% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -2212,58 +2329,9 @@
 []</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-51% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Raunak Khemuka
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2279,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2365,8 +2433,22 @@
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -2375,7 +2457,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -2401,7 +2490,14 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -2413,12 +2509,19 @@
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Anisha Shah
+Bret Saldanha
 32% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2427,16 +2530,7 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2444,6 +2538,8 @@
 []</t>
         </is>
       </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2452,33 +2548,40 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -2507,13 +2610,20 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2523,14 +2633,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -2550,14 +2653,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -2567,13 +2663,20 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Rohan Dahima
-63% pred | 0% hist
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2586,20 +2689,27 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
+Vivaran Dhasmana
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Rohan Dahima
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-69% pred | 0% hist
+38% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2614,14 +2724,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="7" t="inlineStr">
@@ -2641,25 +2744,32 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Reshma Sharma
+Anisha Shah
 44% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
     </row>
@@ -2669,15 +2779,15 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
@@ -2690,9 +2800,9 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Reshma Sharma
-63% pred | 0% hist
+          <t>PowerCycle
+Rohan Dahima
+90% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2721,7 +2831,14 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
@@ -2732,7 +2849,14 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2742,7 +2866,14 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -2773,14 +2904,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -2789,7 +2913,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -2803,48 +2934,43 @@
       <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
-Atulan Purohit
+Reshma Sharma
 79% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2852,16 +2978,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
@@ -2869,30 +2986,37 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -2901,100 +3025,100 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-31% pred | 0% hist
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+67% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+86% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Karan Bhatia
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Karanvir Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
@@ -3002,42 +3126,56 @@
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -3045,33 +3183,40 @@
 []</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Pranjali Jain
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
+Reshma Sharma
 52% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -3079,58 +3224,9 @@
 []</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-51% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Raunak Khemuka
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -51,11 +51,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
+      <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00991B1B"/>
+      <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
     <font>
@@ -106,12 +106,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD5D5"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -643,22 +643,8 @@
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -675,11 +661,11 @@
 []</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-82% pred | 0% hist
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+46% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -691,7 +677,7 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
@@ -700,14 +686,7 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -716,23 +695,16 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -740,16 +712,23 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -767,15 +746,8 @@
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -783,15 +755,15 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Mrigakshi Jaiswal
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -800,7 +772,7 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -816,24 +788,24 @@
 []</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -843,7 +815,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -863,7 +842,14 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -873,20 +859,13 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-55% pred | 0% hist
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -899,31 +878,24 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karanvir Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
@@ -933,10 +905,38 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+70% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -954,34 +954,34 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -989,30 +989,37 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
       </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle
-Rohan Dahima
-90% pred | 0% hist
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1033,7 +1040,7 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1041,14 +1048,7 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
@@ -1059,15 +1059,15 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1076,11 +1076,11 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+0% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1092,7 +1092,14 @@
 []</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -1102,17 +1109,38 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+          <t>FIT
+Rohan Dahima
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
@@ -1123,22 +1151,8 @@
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="5" t="inlineStr">
@@ -1149,46 +1163,60 @@
 []</t>
         </is>
       </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Karan Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
@@ -1196,7 +1224,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
@@ -1204,20 +1232,20 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
@@ -1225,104 +1253,69 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+21% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-86% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-32% pred | 0% hist
+28% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1331,61 +1324,152 @@
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Rohan Dahima
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1393,16 +1477,16 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -1410,7 +1494,7 @@
 []</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -1418,25 +1502,53 @@
 []</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1452,7 +1564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1538,22 +1650,8 @@
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -1570,11 +1668,11 @@
 []</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-82% pred | 0% hist
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+46% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1586,7 +1684,7 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
@@ -1595,14 +1693,7 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -1611,23 +1702,16 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1635,16 +1719,23 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1662,15 +1753,8 @@
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1678,15 +1762,15 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Mrigakshi Jaiswal
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -1695,7 +1779,7 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -1711,24 +1795,24 @@
 []</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -1738,7 +1822,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -1758,7 +1849,14 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1768,20 +1866,13 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-55% pred | 0% hist
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1794,31 +1885,24 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karanvir Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
@@ -1828,10 +1912,38 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+70% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -1849,34 +1961,34 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -1884,30 +1996,37 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
       </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle
-Rohan Dahima
-90% pred | 0% hist
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1928,7 +2047,7 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1936,14 +2055,7 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
@@ -1954,15 +2066,15 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1971,11 +2083,11 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+0% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1987,7 +2099,14 @@
 []</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -1997,17 +2116,38 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+          <t>FIT
+Rohan Dahima
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
@@ -2018,22 +2158,8 @@
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="5" t="inlineStr">
@@ -2044,46 +2170,60 @@
 []</t>
         </is>
       </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Karan Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
@@ -2091,7 +2231,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
@@ -2099,20 +2239,20 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
@@ -2120,104 +2260,69 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+21% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-86% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-32% pred | 0% hist
+28% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2226,61 +2331,152 @@
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Rohan Dahima
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2288,16 +2484,16 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -2305,7 +2501,7 @@
 []</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -2313,25 +2509,53 @@
 []</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2347,7 +2571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2433,22 +2657,8 @@
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -2465,11 +2675,11 @@
 []</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-82% pred | 0% hist
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+46% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2481,7 +2691,7 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
@@ -2490,14 +2700,7 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -2506,23 +2709,16 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2530,16 +2726,23 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2557,15 +2760,8 @@
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2573,15 +2769,15 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Mrigakshi Jaiswal
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -2590,7 +2786,7 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -2606,24 +2802,24 @@
 []</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2633,7 +2829,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -2653,7 +2856,14 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -2663,20 +2873,13 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-55% pred | 0% hist
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2689,31 +2892,24 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karanvir Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
@@ -2723,10 +2919,38 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+70% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -2744,34 +2968,34 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -2779,30 +3003,37 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
       </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle
-Rohan Dahima
-90% pred | 0% hist
+          <t>Mat 57
+Karanvir Bhatia
+88% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2823,7 +3054,7 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2831,14 +3062,7 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
@@ -2849,15 +3073,15 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2866,11 +3090,11 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+0% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2882,7 +3106,14 @@
 []</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -2892,17 +3123,38 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+          <t>FIT
+Rohan Dahima
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
@@ -2913,22 +3165,8 @@
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="5" t="inlineStr">
@@ -2939,46 +3177,60 @@
 []</t>
         </is>
       </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Karan Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
@@ -2986,7 +3238,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
@@ -2994,20 +3246,20 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
@@ -3015,104 +3267,69 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+21% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-86% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-32% pred | 0% hist
+28% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3121,61 +3338,152 @@
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+63% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Rohan Dahima
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -3183,16 +3491,16 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -3200,7 +3508,7 @@
 []</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -3208,25 +3516,53 @@
 []</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -55,13 +55,13 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -111,12 +111,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -181,10 +181,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -653,35 +653,28 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Anisha Shah
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
-89% pred | 0% hist
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+14% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -697,13 +690,20 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
+          <t>PowerCycle Express
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
           <t>PowerCycle
 Vivaran Dhasmana
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -716,19 +716,12 @@
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Mrigakshi Jaiswal
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -747,65 +740,58 @@
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Raunak Khemuka
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Atulan Purohit
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
 Pranjali Jain
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Mrigakshi Jaiswal
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -815,14 +801,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -837,35 +816,21 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-57% pred | 0% hist
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -888,11 +853,11 @@
 []</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-20% pred | 0% hist
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+48% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -900,7 +865,7 @@
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -913,10 +878,10 @@
 []</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
@@ -931,9 +896,9 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+36% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -954,72 +919,44 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+63% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1054,20 +991,13 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1075,31 +1005,17 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -1109,43 +1025,22 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
 Rohan Dahima
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -1153,13 +1048,20 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-79% pred | 0% hist
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+70% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1175,7 +1077,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -1184,89 +1086,89 @@
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+25% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -1274,20 +1176,20 @@
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -1298,8 +1200,8 @@
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-21% pred | 0% hist
+Pranjali Jain
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1308,42 +1210,84 @@
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Bret Saldanha
-41% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1351,24 +1295,24 @@
 []</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
@@ -1376,15 +1320,8 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Raunak Khemuka
@@ -1392,88 +1329,46 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Karan Bhatia
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
 34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1481,44 +1376,44 @@
       <c r="H29" s="6" t="n"/>
     </row>
     <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Karan Bhatia
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-34% pred | 0% hist
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1530,18 +1425,25 @@
       <c r="H31" s="6" t="n"/>
     </row>
     <row r="32" ht="52" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
@@ -1549,6 +1451,97 @@
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1564,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1660,35 +1653,28 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Anisha Shah
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
-89% pred | 0% hist
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+14% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1704,13 +1690,20 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
+          <t>PowerCycle Express
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
           <t>PowerCycle
 Vivaran Dhasmana
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1723,19 +1716,12 @@
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Mrigakshi Jaiswal
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1754,65 +1740,58 @@
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Raunak Khemuka
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Atulan Purohit
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
 Pranjali Jain
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Mrigakshi Jaiswal
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -1822,14 +1801,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -1844,35 +1816,21 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-57% pred | 0% hist
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1895,11 +1853,11 @@
 []</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-20% pred | 0% hist
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+48% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1907,7 +1865,7 @@
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -1920,10 +1878,10 @@
 []</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
@@ -1938,9 +1896,9 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+36% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1961,72 +1919,44 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+63% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2061,20 +1991,13 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2082,31 +2005,17 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -2116,43 +2025,22 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
 Rohan Dahima
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -2160,13 +2048,20 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-79% pred | 0% hist
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+70% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2182,7 +2077,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -2191,89 +2086,89 @@
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+25% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -2281,20 +2176,20 @@
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -2305,8 +2200,8 @@
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-21% pred | 0% hist
+Pranjali Jain
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2315,42 +2210,84 @@
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Bret Saldanha
-41% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2358,24 +2295,24 @@
 []</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
@@ -2383,15 +2320,8 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Raunak Khemuka
@@ -2399,88 +2329,46 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Karan Bhatia
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
 34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2488,44 +2376,44 @@
       <c r="H29" s="6" t="n"/>
     </row>
     <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Karan Bhatia
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-34% pred | 0% hist
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2537,18 +2425,25 @@
       <c r="H31" s="6" t="n"/>
     </row>
     <row r="32" ht="52" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
@@ -2556,6 +2451,97 @@
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2571,7 +2557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2667,35 +2653,28 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Anisha Shah
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
-89% pred | 0% hist
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+14% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2711,13 +2690,20 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
+          <t>PowerCycle Express
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
           <t>PowerCycle
 Vivaran Dhasmana
-10% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2730,19 +2716,12 @@
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Mrigakshi Jaiswal
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2761,65 +2740,58 @@
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Raunak Khemuka
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Atulan Purohit
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
 Pranjali Jain
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Mrigakshi Jaiswal
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2829,14 +2801,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -2851,35 +2816,21 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-57% pred | 0% hist
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2902,11 +2853,11 @@
 []</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-20% pred | 0% hist
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+48% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2914,7 +2865,7 @@
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2927,10 +2878,10 @@
 []</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
@@ -2945,9 +2896,9 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+36% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2968,72 +2919,44 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Mat 57
-Karanvir Bhatia
-88% pred | 0% hist
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+63% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3068,20 +2991,13 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -3089,31 +3005,17 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -3123,43 +3025,22 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
 Rohan Dahima
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -3167,13 +3048,20 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-79% pred | 0% hist
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+70% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3189,7 +3077,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -3198,89 +3086,89 @@
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+25% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -3288,20 +3176,20 @@
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -3312,8 +3200,8 @@
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-21% pred | 0% hist
+Pranjali Jain
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3322,42 +3210,84 @@
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Bret Saldanha
-41% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -3365,24 +3295,24 @@
 []</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Reshma Sharma
@@ -3390,15 +3320,8 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Raunak Khemuka
@@ -3406,88 +3329,46 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Karan Bhatia
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
 34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3495,44 +3376,44 @@
       <c r="H29" s="6" t="n"/>
     </row>
     <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Karan Bhatia
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-34% pred | 0% hist
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3544,18 +3425,25 @@
       <c r="H31" s="6" t="n"/>
     </row>
     <row r="32" ht="52" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
 []</t>
@@ -3563,6 +3451,97 @@
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,11 +51,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00991B1B"/>
+      <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
+      <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -63,12 +63,8 @@
       <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
-    <font>
-      <color rgb="00374151"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -102,22 +98,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -176,9 +167,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -632,14 +620,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
       <c r="F3" s="6" t="n"/>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -648,12 +629,19 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-47% pred | 0% hist
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+13% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -661,11 +649,11 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
@@ -674,7 +662,14 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -683,25 +678,94 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Vivaran Dhasmana
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-85% pred | 0% hist
+86% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
+          <t>Mat 57
 Cauveri Vikrant
-67% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Pranjali Jain
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -709,31 +773,18 @@
 []</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Reshma Sharma
@@ -741,69 +792,6 @@
 []</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-90% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Pranjali Jain
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -812,14 +800,7 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
@@ -830,7 +811,14 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -840,8 +828,22 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
@@ -858,32 +860,32 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
@@ -894,21 +896,14 @@
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-20% pred | 0% hist
+          <t>FIT
+Mrigakshi Jaiswal
+65% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -922,29 +917,29 @@
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -958,24 +953,31 @@
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+62% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -993,19 +995,33 @@
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karanvir Bhatia
-46% pred | 0% hist
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1014,113 +1030,92 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+72% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-72% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
+81% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Reshma Sharma
-79% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-81% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1128,30 +1123,23 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1159,10 +1147,10 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Cauveri Vikrant
 20% pred | 0% hist
 []</t>
         </is>
@@ -1170,14 +1158,7 @@
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -1187,20 +1168,20 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -1208,7 +1189,14 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
@@ -1229,27 +1217,34 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Richard D'Costa
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -1260,11 +1255,11 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-100% pred | 0% hist
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+89% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1288,101 +1283,45 @@
       </c>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Richard D'Costa
+70% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1398,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1485,14 +1424,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
       <c r="F3" s="6" t="n"/>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -1501,12 +1433,19 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-47% pred | 0% hist
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+13% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1514,11 +1453,11 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
@@ -1527,7 +1466,14 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -1536,25 +1482,94 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Vivaran Dhasmana
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-85% pred | 0% hist
+86% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
+          <t>Mat 57
 Cauveri Vikrant
-67% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Pranjali Jain
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -1562,31 +1577,18 @@
 []</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Reshma Sharma
@@ -1594,69 +1596,6 @@
 []</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-90% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Pranjali Jain
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -1665,14 +1604,7 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
@@ -1683,7 +1615,14 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1693,8 +1632,22 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
@@ -1711,32 +1664,32 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
@@ -1747,21 +1700,14 @@
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-20% pred | 0% hist
+          <t>FIT
+Mrigakshi Jaiswal
+65% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1775,29 +1721,29 @@
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -1811,24 +1757,31 @@
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+62% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1846,19 +1799,33 @@
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karanvir Bhatia
-46% pred | 0% hist
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1867,113 +1834,92 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+72% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-72% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
+81% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Reshma Sharma
-79% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-81% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1981,30 +1927,23 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2012,10 +1951,10 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Cauveri Vikrant
 20% pred | 0% hist
 []</t>
         </is>
@@ -2023,14 +1962,7 @@
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -2040,20 +1972,20 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -2061,7 +1993,14 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
@@ -2082,27 +2021,34 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Richard D'Costa
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -2113,11 +2059,11 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-100% pred | 0% hist
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+89% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2141,101 +2087,45 @@
       </c>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Richard D'Costa
+70% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2251,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2338,14 +2228,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
       <c r="F3" s="6" t="n"/>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -2354,12 +2237,19 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-47% pred | 0% hist
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+13% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2367,11 +2257,11 @@
         <is>
           <t>Strength Lab
 Anisha Shah
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Rohan Dahima
@@ -2380,7 +2270,14 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
@@ -2389,25 +2286,94 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Vivaran Dhasmana
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-85% pred | 0% hist
+86% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
+          <t>Mat 57
 Cauveri Vikrant
-67% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Pranjali Jain
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -2415,31 +2381,18 @@
 []</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Reshma Sharma
@@ -2447,69 +2400,6 @@
 []</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-90% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Pranjali Jain
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
@@ -2518,14 +2408,7 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
@@ -2536,7 +2419,14 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -2546,8 +2436,22 @@
 []</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
@@ -2564,32 +2468,32 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
@@ -2600,21 +2504,14 @@
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-20% pred | 0% hist
+          <t>FIT
+Mrigakshi Jaiswal
+65% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2628,29 +2525,29 @@
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -2664,24 +2561,31 @@
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+62% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -2699,19 +2603,33 @@
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+10% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karanvir Bhatia
-46% pred | 0% hist
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2720,113 +2638,92 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+72% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-72% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
+81% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
 Reshma Sharma
-79% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-81% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2834,30 +2731,23 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2865,10 +2755,10 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Cauveri Vikrant
 20% pred | 0% hist
 []</t>
         </is>
@@ -2876,14 +2766,7 @@
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -2893,20 +2776,20 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -2914,7 +2797,14 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
@@ -2935,27 +2825,34 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-20% pred | 0% hist
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Richard D'Costa
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -2966,11 +2863,11 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-100% pred | 0% hist
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+89% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2994,101 +2891,45 @@
       </c>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Richard D'Costa
+70% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Mrigakshi Jaiswal
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anisha Shah
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
